--- a/estimate-sinwa-canopy.xlsx
+++ b/estimate-sinwa-canopy.xlsx
@@ -92,7 +92,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -114,11 +114,55 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -163,6 +207,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -559,6 +605,12 @@
           <t>車寄せ 前方・後方パネル／ルーバー 撤去工事（仮称）</t>
         </is>
       </c>
+      <c r="C3" s="28" t="n"/>
+      <c r="D3" s="28" t="n"/>
+      <c r="E3" s="28" t="n"/>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
+      <c r="H3" s="29" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -571,6 +623,12 @@
           <t>神奈川県横浜市都筑区茅ケ崎南 3-23-5　信和ホームズ㈱ 社屋 車寄せ</t>
         </is>
       </c>
+      <c r="C4" s="28" t="n"/>
+      <c r="D4" s="28" t="n"/>
+      <c r="E4" s="28" t="n"/>
+      <c r="F4" s="28" t="n"/>
+      <c r="G4" s="28" t="n"/>
+      <c r="H4" s="29" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -583,6 +641,12 @@
           <t>2026年9月2日（水）9:00　立会：専務 藤井 様（熊谷組 担当）／社長 古谷 様／会長 園尾 様</t>
         </is>
       </c>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="29" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -595,6 +659,12 @@
           <t>前方パネル（ケイカル板）一部4面 ／ 後方パネル 1面 ／ 奥のルーバー＋下地（鉄骨アングル）の撤去。取合い部シールは先行撤去。撤去後は鉄骨あらわし。</t>
         </is>
       </c>
+      <c r="C6" s="28" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
+      <c r="H6" s="29" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -607,6 +677,12 @@
           <t>道路側：高所作業車　／　敷地内：ローリングタワー　／　営業中（駐車車両の移動・養生あり）</t>
         </is>
       </c>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="29" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -619,6 +695,12 @@
           <t>2026年9月2日　（数量根拠：別シート「数量根拠」）</t>
         </is>
       </c>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="29" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -953,7 +1035,7 @@
         </is>
       </c>
       <c r="D22" s="13">
-        <f>数量根拠!C31</f>
+        <f>数量根拠!C30</f>
         <v/>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -987,7 +1069,7 @@
         </is>
       </c>
       <c r="D23" s="13">
-        <f>数量根拠!C26</f>
+        <f>数量根拠!C25</f>
         <v/>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1021,7 +1103,7 @@
         </is>
       </c>
       <c r="D24" s="13">
-        <f>数量根拠!C27</f>
+        <f>数量根拠!C26</f>
         <v/>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1055,7 +1137,7 @@
         </is>
       </c>
       <c r="D25" s="13">
-        <f>数量根拠!C28</f>
+        <f>数量根拠!C27</f>
         <v/>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1089,7 +1171,7 @@
         </is>
       </c>
       <c r="D26" s="13">
-        <f>数量根拠!C29</f>
+        <f>数量根拠!C28</f>
         <v/>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -1123,7 +1205,7 @@
         </is>
       </c>
       <c r="D27" s="13">
-        <f>数量根拠!C30</f>
+        <f>数量根拠!C29</f>
         <v/>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1694,10 +1776,6 @@
           <t>■ 実測値（書込みより）</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
@@ -1964,10 +2042,6 @@
           <t>■ 仕様（聞取り・書込み）</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -2117,10 +2191,6 @@
           <t>■ 数量計算</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
@@ -2317,7 +2387,7 @@
         </is>
       </c>
       <c r="C31" s="27">
-        <f>C26+C28+C29</f>
+        <f>C25+C27+C28</f>
         <v/>
       </c>
       <c r="D31" s="8" t="inlineStr">
